--- a/docs/files/REPORT_FILTRI/Agente Marcelli Emanuele - CR DI FILIPPO SIMONE.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Marcelli Emanuele - CR DI FILIPPO SIMONE.xlsx
@@ -536,7 +536,7 @@
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,35 +821,35 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>14</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/Agente Marcelli Emanuele - CR DI FILIPPO SIMONE.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Marcelli Emanuele - CR DI FILIPPO SIMONE.xlsx
@@ -536,7 +536,7 @@
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,35 +821,35 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/Agente Marcelli Emanuele - CR DI FILIPPO SIMONE.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Marcelli Emanuele - CR DI FILIPPO SIMONE.xlsx
@@ -536,7 +536,7 @@
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,35 +821,35 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>15</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>270</v>
+        <v>289</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
